--- a/forms/trg/Formulir_TRG_busan.xlsx
+++ b/forms/trg/Formulir_TRG_busan.xlsx
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <f>COUNTA(Anggota!B5:B28)</f>
+        <f>COUNTA(Anggota!B5:B29)</f>
         <v/>
       </c>
     </row>
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="B27" s="7">
-        <f>COUNTA(Anggota!F5:F28)</f>
+        <f>COUNTA(Anggota!F5:F29)</f>
         <v/>
       </c>
     </row>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -937,29 +937,29 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr. Basir Said, MA</t>
+          <t>Dr. Safriadi, SIP, M.Si</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Urban Anthropology</t>
+          <t>Anthropology of Business Organizations</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="12" t="n"/>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-1554-8936</t>
+        </is>
+      </c>
       <c r="K5" s="12" t="n"/>
       <c r="L5" s="12" t="n"/>
       <c r="M5" s="11" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Hardiyanti Munsi, S.Sos, M.Si</t>
+          <t>Dr. Basir Said, MA</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -989,28 +989,16 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Business Antropology</t>
+          <t>Urban Anthropology</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>0009-0006-5425-2707</t>
-        </is>
-      </c>
-      <c r="K6" s="11" t="inlineStr">
-        <is>
-          <t>6749864</t>
-        </is>
-      </c>
-      <c r="L6" s="11" t="inlineStr">
-        <is>
-          <t>57212146233</t>
-        </is>
-      </c>
+      <c r="J6" s="12" t="n"/>
+      <c r="K6" s="12" t="n"/>
+      <c r="L6" s="12" t="n"/>
       <c r="M6" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1023,12 +1011,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ahmad Ismail, S.Sos, MSi</t>
+          <t>Hardiyanti Munsi, S.Sos, M.Si</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1036,14 +1024,30 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E7" s="11" t="n"/>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Business Antropology</t>
+        </is>
+      </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
-      <c r="J7" s="12" t="n"/>
-      <c r="K7" s="12" t="n"/>
-      <c r="L7" s="12" t="n"/>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>0009-0006-5425-2707</t>
+        </is>
+      </c>
+      <c r="K7" s="11" t="inlineStr">
+        <is>
+          <t>6749864</t>
+        </is>
+      </c>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>57212146233</t>
+        </is>
+      </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1056,24 +1060,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Tasrifin Tahara, MSi</t>
+          <t>Dr. Ahmad Ismail, S.Sos, MSi</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin Uninersity</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>Anthropologi of Power</t>
-        </is>
-      </c>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="n"/>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
@@ -1093,22 +1093,22 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Tanuz Kalita, MA</t>
+          <t>Prof. Dr. Tasrifin Tahara, MSi</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru University</t>
+          <t>Hasanuddin Uninersity</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Indigenous People</t>
+          <t>Anthropologi of Power</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1130,22 +1130,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Mahadirin Hj. Ahmad</t>
+          <t>Tanuz Kalita, MA</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>University of Malaysia Sabah</t>
+          <t>Jawaharlal Nehru University</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Industrial Relations and Collective Action</t>
+          <t>Indigenous People</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1167,20 +1167,24 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Andi Batara Al Isra, S.Sos, MA</t>
+          <t>Mahadirin Hj. Ahmad</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="n"/>
+          <t>University of Malaysia Sabah</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Industrial Relations and Collective Action</t>
+        </is>
+      </c>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
@@ -1200,24 +1204,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Andi Muh. Yusuf, S.Sos, M.Si</t>
+          <t>Andi Batara Al Isra, S.Sos, MA</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Universitas Islam Negeri Mataram</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>Indigenous People</t>
-        </is>
-      </c>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="n"/>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
@@ -1237,39 +1237,31 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Jayana Suryana Kembara, S.Sos, M.Si</t>
+          <t>Andi Muh. Yusuf, S.Sos, M.Si</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Universitas Islam Negeri Mataram</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Urban Anthropology</t>
+          <t>Indigenous People</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
       <c r="I13" s="12" t="n"/>
-      <c r="J13" s="11" t="inlineStr">
-        <is>
-          <t>my-orcid?orcid=0009-0001-8692-3222</t>
-        </is>
-      </c>
+      <c r="J13" s="12" t="n"/>
       <c r="K13" s="12" t="n"/>
-      <c r="L13" s="11" t="inlineStr">
-        <is>
-          <t>60006414200</t>
-        </is>
-      </c>
+      <c r="L13" s="12" t="n"/>
       <c r="M13" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1282,12 +1274,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Wahyu Chandra, S.IP., M.Si</t>
+          <t>Jayana Suryana Kembara, S.Sos, M.Si</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1295,14 +1287,26 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E14" s="11" t="n"/>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>Urban Anthropology</t>
+        </is>
+      </c>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
       <c r="I14" s="12" t="n"/>
-      <c r="J14" s="12" t="n"/>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>my-orcid?orcid=0009-0001-8692-3222</t>
+        </is>
+      </c>
       <c r="K14" s="12" t="n"/>
-      <c r="L14" s="12" t="n"/>
+      <c r="L14" s="11" t="inlineStr">
+        <is>
+          <t>60006414200</t>
+        </is>
+      </c>
       <c r="M14" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1315,12 +1319,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Muh. Fadlan</t>
+          <t>Wahyu Chandra, S.IP., M.Si</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1348,15 +1352,19 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Ainun Syafitri Muslimin</t>
+          <t>Muh. Fadlan</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="n"/>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
       <c r="E16" s="11" t="n"/>
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="12" t="n"/>
@@ -1375,8 +1383,16 @@
       <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Ainun Syafitri Muslimin</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D17" s="12" t="n"/>
       <c r="E17" s="11" t="n"/>
       <c r="F17" s="12" t="n"/>
@@ -1386,7 +1402,11 @@
       <c r="J17" s="12" t="n"/>
       <c r="K17" s="12" t="n"/>
       <c r="L17" s="12" t="n"/>
-      <c r="M17" s="12" t="n"/>
+      <c r="M17" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -1575,15 +1595,32 @@
       <c r="L28" s="12" t="n"/>
       <c r="M28" s="12" t="n"/>
     </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="12" t="n"/>
+      <c r="C29" s="12" t="n"/>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="12" t="n"/>
+      <c r="G29" s="12" t="n"/>
+      <c r="H29" s="12" t="n"/>
+      <c r="I29" s="12" t="n"/>
+      <c r="J29" s="12" t="n"/>
+      <c r="K29" s="12" t="n"/>
+      <c r="L29" s="12" t="n"/>
+      <c r="M29" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
